--- a/Result/profitability/3167.xlsx
+++ b/Result/profitability/3167.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM66"/>
+  <dimension ref="A1:AM67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.81</v>
       </c>
       <c r="M2" t="n">
-        <v>1.9375</v>
+        <v>2.635</v>
       </c>
       <c r="N2" t="n">
-        <v>36.22625</v>
+        <v>37.85125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.27</v>
       </c>
       <c r="M3" t="n">
-        <v>2.03125</v>
+        <v>2.6875</v>
       </c>
       <c r="N3" t="n">
-        <v>35.4875</v>
+        <v>36.9775</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.09</v>
       </c>
       <c r="M4" t="n">
-        <v>2.06125</v>
+        <v>2.69625</v>
       </c>
       <c r="N4" t="n">
-        <v>34.57375</v>
+        <v>35.81375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>1.97</v>
+        <v>2.48375</v>
       </c>
       <c r="N5" t="n">
-        <v>34.1325</v>
+        <v>34.8</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.89625</v>
+        <v>2.35375</v>
       </c>
       <c r="N6" t="n">
-        <v>32.93375</v>
+        <v>33.56625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>3.02</v>
       </c>
       <c r="M7" t="n">
-        <v>1.96875</v>
+        <v>2.39625</v>
       </c>
       <c r="N7" t="n">
-        <v>31.5725</v>
+        <v>31.8325</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8810,6 +8810,133 @@
       </c>
       <c r="AM66" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2859</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1595</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1264</v>
+      </c>
+      <c r="F67" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G67" t="n">
+        <v>767</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>26.82%</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>9</v>
+      </c>
+      <c r="J67" t="n">
+        <v>776</v>
+      </c>
+      <c r="K67" t="n">
+        <v>543</v>
+      </c>
+      <c r="L67" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2.34875</v>
+      </c>
+      <c r="N67" t="n">
+        <v>38.0525</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0.9122257053291536</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>1.859999999999999</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.04393008974964574</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>4.109999999999999</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>2.065326633165829</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>5.340000000000003</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.1374163664436439</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK67" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
